--- a/output/quickfixopen_all_markets_daily.xlsx
+++ b/output/quickfixopen_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-28 22:50 UTC.</t>
+          <t>quickfixopen daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen_all_markets_daily.xlsx
+++ b/output/quickfixopen_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -735,28 +735,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -771,40 +771,40 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>8.1</v>
+        <v>9.34</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>108098.31</v>
+        <v>109335.15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7.71</v>
+        <v>8.1</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>107706.09</v>
+        <v>108098.31</v>
       </c>
     </row>
     <row r="8">
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>100</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-27); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-29 02:46 UTC.</t>
+          <t>quickfixopen daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-29); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-30 20:33 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5628,11 +5628,11 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5641,42 +5641,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1</v>
+          <t>2026-07-29</t>
+        </is>
       </c>
       <c r="G57" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H57" t="n">
-        <v>1343.4</v>
-      </c>
-      <c r="J57" t="n">
-        <v>1403</v>
+        <v>2.665</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>2.5059</v>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>2.5059</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N57" t="n">
-        <v>100000</v>
+        <v>102474.86</v>
       </c>
       <c r="O57" t="n">
-        <v>102505.88</v>
+        <v>102474.86</v>
       </c>
     </row>
     <row r="58">
@@ -5686,7 +5669,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5695,25 +5678,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H58" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J58" t="n">
-        <v>1185</v>
+        <v>1403</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5721,53 +5704,53 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="N58" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O58" t="n">
         <v>102505.88</v>
-      </c>
-      <c r="O58" t="n">
-        <v>104933.65</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H59" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J59" t="n">
-        <v>2031.1</v>
+        <v>1185</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5775,16 +5758,16 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>102505.88</v>
       </c>
       <c r="O59" t="n">
-        <v>101838.49</v>
+        <v>104933.65</v>
       </c>
     </row>
     <row r="60">
@@ -5794,34 +5777,34 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H60" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J60" t="n">
-        <v>1651</v>
+        <v>2031.1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5829,16 +5812,16 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0.4634</v>
+        <v>1.8385</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.4634</v>
+        <v>1.8385</v>
       </c>
       <c r="N60" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O60" t="n">
         <v>101838.49</v>
-      </c>
-      <c r="O60" t="n">
-        <v>102310.42</v>
       </c>
     </row>
     <row r="61">
@@ -5848,7 +5831,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -5857,25 +5840,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J61" t="n">
-        <v>1618.8</v>
+        <v>1651</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5883,16 +5866,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.1003</v>
+        <v>0.4634</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.1003</v>
+        <v>0.4634</v>
       </c>
       <c r="N61" t="n">
+        <v>101838.49</v>
+      </c>
+      <c r="O61" t="n">
         <v>102310.42</v>
-      </c>
-      <c r="O61" t="n">
-        <v>103436.14</v>
       </c>
     </row>
     <row r="62">
@@ -5902,7 +5885,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5911,25 +5894,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="J62" t="n">
-        <v>1586.6</v>
+        <v>1618.8</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5937,53 +5920,53 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.4154</v>
+        <v>1.1003</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1.4154</v>
+        <v>1.1003</v>
       </c>
       <c r="N62" t="n">
+        <v>102310.42</v>
+      </c>
+      <c r="O62" t="n">
         <v>103436.14</v>
-      </c>
-      <c r="O62" t="n">
-        <v>104900.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H63" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J63" t="n">
-        <v>27760</v>
+        <v>1586.6</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5991,22 +5974,22 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="N63" t="n">
-        <v>100000</v>
+        <v>103436.14</v>
       </c>
       <c r="O63" t="n">
-        <v>102501.7</v>
+        <v>104900.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6019,25 +6002,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>7206.55</v>
+        <v>27907</v>
       </c>
       <c r="H64" t="n">
-        <v>7223.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J64" t="n">
-        <v>7172.5</v>
+        <v>27760</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6045,22 +6028,22 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.0377</v>
+        <v>2.5017</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.0377</v>
+        <v>2.5017</v>
       </c>
       <c r="N64" t="n">
         <v>100000</v>
       </c>
       <c r="O64" t="n">
-        <v>102037.7</v>
+        <v>102501.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6073,25 +6056,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>6957.43</v>
+        <v>7206.55</v>
       </c>
       <c r="H65" t="n">
-        <v>6965.7</v>
+        <v>7223.26</v>
       </c>
       <c r="J65" t="n">
-        <v>6914.11</v>
+        <v>7172.5</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6099,16 +6082,16 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>5.2382</v>
+        <v>2.0377</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5.2382</v>
+        <v>2.0377</v>
       </c>
       <c r="N65" t="n">
         <v>100000</v>
       </c>
       <c r="O65" t="n">
-        <v>105238.21</v>
+        <v>102037.7</v>
       </c>
     </row>
     <row r="66">
@@ -6118,7 +6101,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -6127,25 +6110,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H66" t="n">
-        <v>6988.83</v>
+        <v>6965.7</v>
       </c>
       <c r="J66" t="n">
-        <v>7002</v>
+        <v>6914.11</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6153,16 +6136,16 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M66" s="10" t="n">
-        <v>-3.0482</v>
+        <v>5.2382</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>5.2382</v>
       </c>
       <c r="N66" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O66" t="n">
         <v>105238.21</v>
-      </c>
-      <c r="O66" t="n">
-        <v>102030.33</v>
       </c>
     </row>
     <row r="67">
@@ -6172,7 +6155,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6181,12 +6164,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -6196,10 +6179,10 @@
         <v>6982.4</v>
       </c>
       <c r="H67" t="n">
-        <v>6992.85</v>
+        <v>6988.83</v>
       </c>
       <c r="J67" t="n">
-        <v>6947.27</v>
+        <v>7002</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6207,16 +6190,16 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.3617</v>
-      </c>
-      <c r="M67" s="2" t="n">
-        <v>3.3617</v>
+        <v>-3.0482</v>
+      </c>
+      <c r="M67" s="10" t="n">
+        <v>-3.0482</v>
       </c>
       <c r="N67" t="n">
+        <v>105238.21</v>
+      </c>
+      <c r="O67" t="n">
         <v>102030.33</v>
-      </c>
-      <c r="O67" t="n">
-        <v>105460.3</v>
       </c>
     </row>
     <row r="68">
@@ -6226,7 +6209,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6235,12 +6218,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -6250,10 +6233,10 @@
         <v>6982.4</v>
       </c>
       <c r="H68" t="n">
-        <v>6991.93</v>
+        <v>6992.85</v>
       </c>
       <c r="J68" t="n">
-        <v>6985.45</v>
+        <v>6947.27</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6261,16 +6244,16 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="M68" s="10" t="n">
-        <v>-0.32</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>3.3617</v>
       </c>
       <c r="N68" t="n">
+        <v>102030.33</v>
+      </c>
+      <c r="O68" t="n">
         <v>105460.3</v>
-      </c>
-      <c r="O68" t="n">
-        <v>105122.79</v>
       </c>
     </row>
     <row r="69">
@@ -6280,7 +6263,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6289,12 +6272,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -6304,10 +6287,10 @@
         <v>6982.4</v>
       </c>
       <c r="H69" t="n">
-        <v>6986.84</v>
+        <v>6991.93</v>
       </c>
       <c r="J69" t="n">
-        <v>6976.48</v>
+        <v>6985.45</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6315,16 +6298,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>1.3333</v>
-      </c>
-      <c r="M69" s="2" t="n">
-        <v>1.3333</v>
+        <v>-0.32</v>
+      </c>
+      <c r="M69" s="10" t="n">
+        <v>-0.32</v>
       </c>
       <c r="N69" t="n">
+        <v>105460.3</v>
+      </c>
+      <c r="O69" t="n">
         <v>105122.79</v>
-      </c>
-      <c r="O69" t="n">
-        <v>106524.42</v>
       </c>
     </row>
     <row r="70">
@@ -6334,34 +6317,34 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H70" t="n">
-        <v>6770.77</v>
+        <v>6986.84</v>
       </c>
       <c r="J70" t="n">
-        <v>6769.03</v>
+        <v>6976.48</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6369,53 +6352,53 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M70" s="10" t="n">
-        <v>-1.0736</v>
+        <v>1.3333</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>1.3333</v>
       </c>
       <c r="N70" t="n">
+        <v>105122.79</v>
+      </c>
+      <c r="O70" t="n">
         <v>106524.42</v>
-      </c>
-      <c r="O70" t="n">
-        <v>105380.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>86.081</v>
+        <v>6794.4</v>
       </c>
       <c r="H71" t="n">
-        <v>88.001</v>
+        <v>6770.77</v>
       </c>
       <c r="J71" t="n">
-        <v>87.31999999999999</v>
+        <v>6769.03</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6423,16 +6406,16 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-0.6453</v>
+        <v>-1.0736</v>
       </c>
       <c r="M71" s="10" t="n">
-        <v>-0.6453</v>
+        <v>-1.0736</v>
       </c>
       <c r="N71" t="n">
-        <v>100000</v>
+        <v>106524.42</v>
       </c>
       <c r="O71" t="n">
-        <v>99354.69</v>
+        <v>105380.74</v>
       </c>
     </row>
     <row r="72">
@@ -6442,34 +6425,34 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>73.84399999999999</v>
+        <v>86.081</v>
       </c>
       <c r="H72" t="n">
-        <v>71.999</v>
+        <v>88.001</v>
       </c>
       <c r="J72" t="n">
-        <v>75.565</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6477,53 +6460,53 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0.9328</v>
-      </c>
-      <c r="M72" s="2" t="n">
-        <v>0.9328</v>
+        <v>-0.6453</v>
+      </c>
+      <c r="M72" s="10" t="n">
+        <v>-0.6453</v>
       </c>
       <c r="N72" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O72" t="n">
         <v>99354.69</v>
-      </c>
-      <c r="O72" t="n">
-        <v>100281.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>15</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>15.26</v>
+        <v>71.999</v>
       </c>
       <c r="J73" t="n">
-        <v>15</v>
+        <v>75.565</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6531,22 +6514,22 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="4" t="n">
-        <v>0</v>
+        <v>0.9328</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>0.9328</v>
       </c>
       <c r="N73" t="n">
-        <v>100000</v>
+        <v>99354.69</v>
       </c>
       <c r="O73" t="n">
-        <v>100000</v>
+        <v>100281.46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6559,25 +6542,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>20.89</v>
+        <v>15</v>
       </c>
       <c r="H74" t="n">
-        <v>21.07</v>
+        <v>15.26</v>
       </c>
       <c r="J74" t="n">
-        <v>21.08</v>
+        <v>15</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6585,22 +6568,22 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>-1.0556</v>
-      </c>
-      <c r="M74" s="10" t="n">
-        <v>-1.0556</v>
+        <v>0</v>
+      </c>
+      <c r="M74" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N74" t="n">
         <v>100000</v>
       </c>
       <c r="O74" t="n">
-        <v>98944.44</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6613,25 +6596,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8614000000000001</v>
+        <v>20.89</v>
       </c>
       <c r="H75" t="n">
-        <v>0.8637</v>
+        <v>21.07</v>
       </c>
       <c r="J75" t="n">
-        <v>0.8594000000000001</v>
+        <v>21.08</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6639,16 +6622,16 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0.8696</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>0.8696</v>
+        <v>-1.0556</v>
+      </c>
+      <c r="M75" s="10" t="n">
+        <v>-1.0556</v>
       </c>
       <c r="N75" t="n">
         <v>100000</v>
       </c>
       <c r="O75" t="n">
-        <v>100869.57</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="76">
@@ -6658,7 +6641,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6667,12 +6650,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -6682,10 +6665,10 @@
         <v>0.8614000000000001</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8658</v>
+        <v>0.8637</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8602</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6693,16 +6676,16 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.2727</v>
+        <v>0.8696</v>
       </c>
       <c r="M76" s="2" t="n">
-        <v>0.2727</v>
+        <v>0.8696</v>
       </c>
       <c r="N76" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O76" t="n">
         <v>100869.57</v>
-      </c>
-      <c r="O76" t="n">
-        <v>101144.66</v>
       </c>
     </row>
     <row r="77">
@@ -6712,105 +6695,105 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8467</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8436</v>
+        <v>0.8658</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8498</v>
+        <v>0.8602</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0.2727</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1</v>
+        <v>0.2727</v>
       </c>
       <c r="N77" t="n">
+        <v>100869.57</v>
+      </c>
+      <c r="O77" t="n">
         <v>101144.66</v>
-      </c>
-      <c r="O77" t="n">
-        <v>102156.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>116.5</v>
+        <v>0.8467</v>
       </c>
       <c r="H78" t="n">
-        <v>116.79</v>
+        <v>0.8436</v>
       </c>
       <c r="J78" t="n">
-        <v>116.15</v>
+        <v>0.8498</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.2069</v>
+        <v>1</v>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1.2069</v>
+        <v>1</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>101144.66</v>
       </c>
       <c r="O78" t="n">
-        <v>101206.9</v>
+        <v>102156.11</v>
       </c>
     </row>
     <row r="79">
@@ -6820,7 +6803,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -6829,25 +6812,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>118.02</v>
+        <v>116.5</v>
       </c>
       <c r="H79" t="n">
-        <v>118.16</v>
+        <v>116.79</v>
       </c>
       <c r="J79" t="n">
-        <v>117.9</v>
+        <v>116.15</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6855,16 +6838,16 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0.8571</v>
+        <v>1.2069</v>
       </c>
       <c r="M79" s="2" t="n">
-        <v>0.8571</v>
+        <v>1.2069</v>
       </c>
       <c r="N79" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O79" t="n">
         <v>101206.9</v>
-      </c>
-      <c r="O79" t="n">
-        <v>102074.38</v>
       </c>
     </row>
     <row r="80">
@@ -6874,7 +6857,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6883,25 +6866,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>118.08</v>
+        <v>118.02</v>
       </c>
       <c r="H80" t="n">
         <v>118.16</v>
       </c>
       <c r="J80" t="n">
-        <v>117.87</v>
+        <v>117.9</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6909,53 +6892,53 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.625</v>
+        <v>0.8571</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>2.625</v>
+        <v>0.8571</v>
       </c>
       <c r="N80" t="n">
+        <v>101206.9</v>
+      </c>
+      <c r="O80" t="n">
         <v>102074.38</v>
-      </c>
-      <c r="O80" t="n">
-        <v>104753.84</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>97.81399999999999</v>
+        <v>118.08</v>
       </c>
       <c r="H81" t="n">
-        <v>97.569</v>
+        <v>118.16</v>
       </c>
       <c r="J81" t="n">
-        <v>98</v>
+        <v>117.87</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6963,16 +6946,16 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.7592</v>
+        <v>2.625</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>0.7592</v>
+        <v>2.625</v>
       </c>
       <c r="N81" t="n">
-        <v>100000</v>
+        <v>102074.38</v>
       </c>
       <c r="O81" t="n">
-        <v>100759.18</v>
+        <v>104753.84</v>
       </c>
     </row>
     <row r="82">
@@ -6982,7 +6965,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6991,25 +6974,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F82" t="n">
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>97.714</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>97.46899999999999</v>
+        <v>97.569</v>
       </c>
       <c r="J82" t="n">
-        <v>97.905</v>
+        <v>98</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -7017,16 +7000,16 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.7796</v>
+        <v>0.7592</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.7796</v>
+        <v>0.7592</v>
       </c>
       <c r="N82" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O82" t="n">
         <v>100759.18</v>
-      </c>
-      <c r="O82" t="n">
-        <v>101544.69</v>
       </c>
     </row>
     <row r="83">
@@ -7036,34 +7019,34 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>99.376</v>
+        <v>97.714</v>
       </c>
       <c r="H83" t="n">
-        <v>99.571</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J83" t="n">
-        <v>99.095</v>
+        <v>97.905</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7071,16 +7054,16 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.441</v>
+        <v>0.7796</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1.441</v>
+        <v>0.7796</v>
       </c>
       <c r="N83" t="n">
+        <v>100759.18</v>
+      </c>
+      <c r="O83" t="n">
         <v>101544.69</v>
-      </c>
-      <c r="O83" t="n">
-        <v>103007.98</v>
       </c>
     </row>
     <row r="84">
@@ -7090,7 +7073,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7099,25 +7082,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>99.246</v>
+        <v>99.376</v>
       </c>
       <c r="H84" t="n">
-        <v>99.501</v>
+        <v>99.571</v>
       </c>
       <c r="J84" t="n">
-        <v>98.87</v>
+        <v>99.095</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7125,16 +7108,16 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.4745</v>
+        <v>1.441</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1.4745</v>
+        <v>1.441</v>
       </c>
       <c r="N84" t="n">
+        <v>101544.69</v>
+      </c>
+      <c r="O84" t="n">
         <v>103007.98</v>
-      </c>
-      <c r="O84" t="n">
-        <v>104526.84</v>
       </c>
     </row>
     <row r="85">
@@ -7144,7 +7127,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7153,25 +7136,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H85" t="n">
-        <v>100.201</v>
+        <v>99.501</v>
       </c>
       <c r="J85" t="n">
-        <v>100.045</v>
+        <v>98.87</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7179,16 +7162,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0.1556</v>
+        <v>1.4745</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>0.1556</v>
+        <v>1.4745</v>
       </c>
       <c r="N85" t="n">
+        <v>103007.98</v>
+      </c>
+      <c r="O85" t="n">
         <v>104526.84</v>
-      </c>
-      <c r="O85" t="n">
-        <v>104689.44</v>
       </c>
     </row>
     <row r="86">
@@ -7198,7 +7181,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -7207,12 +7190,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -7222,10 +7205,10 @@
         <v>100.066</v>
       </c>
       <c r="H86" t="n">
-        <v>100.316</v>
+        <v>100.201</v>
       </c>
       <c r="J86" t="n">
-        <v>99.45999999999999</v>
+        <v>100.045</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7233,16 +7216,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.424</v>
+        <v>0.1556</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2.424</v>
+        <v>0.1556</v>
       </c>
       <c r="N86" t="n">
+        <v>104526.84</v>
+      </c>
+      <c r="O86" t="n">
         <v>104689.44</v>
-      </c>
-      <c r="O86" t="n">
-        <v>107227.11</v>
       </c>
     </row>
     <row r="87">
@@ -7252,7 +7235,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -7261,12 +7244,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -7276,10 +7259,10 @@
         <v>100.066</v>
       </c>
       <c r="H87" t="n">
-        <v>100.361</v>
+        <v>100.316</v>
       </c>
       <c r="J87" t="n">
-        <v>100.15</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7287,16 +7270,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>-0.2847</v>
-      </c>
-      <c r="M87" s="10" t="n">
-        <v>-0.2847</v>
+        <v>2.424</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>2.424</v>
       </c>
       <c r="N87" t="n">
+        <v>104689.44</v>
+      </c>
+      <c r="O87" t="n">
         <v>107227.11</v>
-      </c>
-      <c r="O87" t="n">
-        <v>106921.79</v>
       </c>
     </row>
     <row r="88">
@@ -7306,7 +7289,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7315,25 +7298,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H88" t="n">
-        <v>100.911</v>
+        <v>100.361</v>
       </c>
       <c r="J88" t="n">
-        <v>100.7</v>
+        <v>100.15</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7341,16 +7324,16 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-0.2724</v>
+        <v>-0.2847</v>
       </c>
       <c r="M88" s="10" t="n">
-        <v>-0.2724</v>
+        <v>-0.2847</v>
       </c>
       <c r="N88" t="n">
+        <v>107227.11</v>
+      </c>
+      <c r="O88" t="n">
         <v>106921.79</v>
-      </c>
-      <c r="O88" t="n">
-        <v>106630.52</v>
       </c>
     </row>
     <row r="89">
@@ -7360,7 +7343,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7369,25 +7352,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>101.411</v>
+        <v>100.621</v>
       </c>
       <c r="H89" t="n">
-        <v>101.526</v>
+        <v>100.911</v>
       </c>
       <c r="J89" t="n">
-        <v>101.295</v>
+        <v>100.7</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7395,26 +7378,26 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.0087</v>
-      </c>
-      <c r="M89" s="2" t="n">
-        <v>1.0087</v>
+        <v>-0.2724</v>
+      </c>
+      <c r="M89" s="10" t="n">
+        <v>-0.2724</v>
       </c>
       <c r="N89" t="n">
+        <v>106921.79</v>
+      </c>
+      <c r="O89" t="n">
         <v>106630.52</v>
-      </c>
-      <c r="O89" t="n">
-        <v>107706.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7423,25 +7406,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>121.72</v>
+        <v>101.411</v>
       </c>
       <c r="H90" t="n">
-        <v>123.03</v>
+        <v>101.526</v>
       </c>
       <c r="J90" t="n">
-        <v>113.29</v>
+        <v>101.295</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7449,69 +7432,177 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>6.4351</v>
+        <v>1.0087</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>6.4351</v>
+        <v>1.0087</v>
       </c>
       <c r="N90" t="n">
-        <v>100000</v>
+        <v>106630.52</v>
       </c>
       <c r="O90" t="n">
-        <v>106435.11</v>
+        <v>107706.09</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>10</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H91" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J91" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="N91" t="n">
+        <v>107706.09</v>
+      </c>
+      <c r="O91" t="n">
+        <v>109335.15</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B91" t="n">
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H92" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J92" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N92" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O92" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
         <v>2</v>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" t="n">
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
         <v>130.16</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H93" t="n">
         <v>130.94</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J93" t="n">
         <v>124.86</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L91" t="n">
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
         <v>6.7949</v>
       </c>
-      <c r="M91" s="2" t="n">
+      <c r="M93" s="2" t="n">
         <v>6.7949</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N93" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O93" t="n">
         <v>113667.24</v>
       </c>
     </row>
